--- a/pipeline/credit_rating/output/sniratings_xhtn_20261028.xlsx
+++ b/pipeline/credit_rating/output/sniratings_xhtn_20261028.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R2" s="1" t="n">
@@ -637,7 +637,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R3" s="1" t="n">
@@ -701,7 +701,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R4" s="1" t="n">
@@ -773,7 +773,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R5" s="1" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R6" s="1" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R7" s="1" t="n">
@@ -977,7 +977,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R8" s="1" t="n">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R9" s="1" t="n">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R10" s="1" t="n">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R11" s="1" t="n">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R12" s="1" t="n">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R13" s="1" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R14" s="1" t="n">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R15" s="1" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-28 09:58:53</t>
+          <t>2026-10-28 15:22:12</t>
         </is>
       </c>
       <c r="R16" s="1" t="n">
